--- a/update_template.xlsx
+++ b/update_template.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M1 - Reading Paragraph" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2 - Story Building" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M3 - QA Bursts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M4 - Presentation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M5 - Tongue Twisters" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M6 - Poems" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M7 - Silly Debate" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M8 - Audio Postcards" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M1 - Reading Paragraph" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M2 - Story Building" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M3 - QA Bursts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M4 - Presentation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M5 - Tongue Twisters" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M6 - Poems" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M7 - Silly Debate" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M8 - Audio Postcards" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +36,13 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
     </font>
     <font>
       <i val="1"/>
@@ -71,14 +79,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -446,6 +456,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ee42009d-d83e-4c12-abd1-2d8fff809b18</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>UUID of the teacher who created the lessons</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TEACHER</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Role filter  (e.g. TEACHER)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EASY</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Difficulty level  (e.g. EASY, MEDIUM, HARD)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -471,18 +568,18 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="40" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>(example lesson name — delete this row)</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>New passage text here...</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>New example text here...</t>
         </is>
@@ -493,7 +590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -530,23 +627,23 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="40" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>(example lesson name — delete this row)</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>New example question?</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>New example content...</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>word1, word2, word3</t>
         </is>
@@ -557,7 +654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -600,28 +697,28 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="40" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>(example lesson name — delete this row)</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>New theme topic...</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Question 1?.Question 2?.Question 3?</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>New example heading...</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>New example content...</t>
         </is>
@@ -632,7 +729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -675,83 +772,30 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="40" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>(example lesson name — delete this row)</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>New topic overview...</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Guideline 1.Guideline 2.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>New example heading...</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>New example content...</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>lesson_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>example</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tongue_twister</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>(example lesson name — delete this row)</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>New example text here...</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>New tongue twister text...</t>
         </is>
       </c>
     </row>
@@ -787,24 +831,24 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>assigned_text</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
+          <t>tongue_twister</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>(example lesson name — delete this row)</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>New example text here...</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>New poem text here...</t>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>New tongue twister text...</t>
         </is>
       </c>
     </row>
@@ -814,6 +858,59 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>lesson_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>assigned_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>(example lesson name — delete this row)</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>New example text here...</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>New poem text here...</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -874,43 +971,43 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="40" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>(example lesson name — delete this row)</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>New debate topic statement.</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Side the student argues for.</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Side the AI argues for.</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Debate prompt / conversation starter.</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Ice Cream is better than Pizza</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Ice cream is cold and sweet...</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Pizza has cheese and toppings...</t>
         </is>
@@ -921,7 +1018,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -970,33 +1067,33 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customFormat="1" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="40" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>(example lesson name — delete this row)</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>New debate topic statement.</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>New instructions text...</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Ice Cream is better than Pizza</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>New example instruction...</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>New example content...</t>
         </is>
